--- a/frontend/public/bachelor_bct_test_data.xlsx
+++ b/frontend/public/bachelor_bct_test_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,130 +416,148 @@
         <v>Batch</v>
       </c>
       <c r="F1" t="str">
+        <v>Cluster</v>
+      </c>
+      <c r="G1" t="str">
         <v>Supervisor</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>External Examiner</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TeamAlpha</v>
+        <v>BCT-083-G1</v>
       </c>
       <c r="B2" t="str">
-        <v>AI-Powered Smart Farming System</v>
+        <v>IoT-Based Smart Water Quality Monitoring System for Kathmandu Valley</v>
       </c>
       <c r="C2" t="str">
-        <v>Ram Acharya, Shyam Basnet, Hari Chhetri</v>
+        <v>Aashish Khadka, Bimala Neupane, Chiran Rai</v>
       </c>
       <c r="D2" t="str">
-        <v>078BCT001, 078BCT002, 078BCT003</v>
+        <v>083BCT001, 083BCT002, 083BCT003</v>
       </c>
       <c r="E2" t="str">
-        <v>078</v>
+        <v>083</v>
       </c>
       <c r="F2" t="str">
-        <v>Prof. Dr. Rajan Sharma</v>
+        <v>AIML</v>
       </c>
       <c r="G2" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+        <v>Prof. Dr. Dinesh Koirala</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Dr. Anisha Rana</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TeamBeta</v>
+        <v>BCT-083-G2</v>
       </c>
       <c r="B3" t="str">
-        <v>Blockchain Academic Record System</v>
+        <v>Nepali Sign Language Recognition Using Deep Learning</v>
       </c>
       <c r="C3" t="str">
-        <v>Sita Dahal, Gita Gurung, Rita Khadka</v>
+        <v>Dikshya Poudel, Emraj Bhandari</v>
       </c>
       <c r="D3" t="str">
-        <v>078BCT004, 078BCT005, 078BCT006</v>
+        <v>083BCT004, 083BCT005</v>
       </c>
       <c r="E3" t="str">
-        <v>078</v>
+        <v>083</v>
       </c>
       <c r="F3" t="str">
-        <v>Asst. Prof. Sagar Ojha</v>
+        <v>IPCV</v>
       </c>
       <c r="G3" t="str">
-        <v>Dr. Sagar Khanal</v>
+        <v>Assoc. Prof. Dr. Meena Shrestha</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Dr. Bidur Khadka</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TeamGamma</v>
+        <v>BCT-083-G3</v>
       </c>
       <c r="B4" t="str">
-        <v>Real-Time Health Monitoring Wearable</v>
+        <v>Online Blood Donation Management System</v>
       </c>
       <c r="C4" t="str">
-        <v>Krishna Lama, Bishnu Maharjan, Arjun Neupane</v>
+        <v>Fulmaya Dhakal, Gaurav Karki, Himal Maskey</v>
       </c>
       <c r="D4" t="str">
-        <v>078BCT007, 078BCT008, 078BCT009</v>
+        <v>083BCT006, 083BCT007, 083BCT008</v>
       </c>
       <c r="E4" t="str">
-        <v>078</v>
+        <v>083</v>
       </c>
       <c r="F4" t="str">
-        <v>Dr. Anish Pandey</v>
+        <v>ANLP</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Dr. Kiran Adhikari</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Assoc. Prof. Dr. Manisha Aryal</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TeamDelta</v>
+        <v>BCT-083-G4</v>
       </c>
       <c r="B5" t="str">
-        <v>NLP Document Summarization Tool</v>
+        <v>Smart Traffic Signal Control Using Computer Vision</v>
       </c>
       <c r="C5" t="str">
-        <v>Pratik Ojha, Nabin Pandey, Sagar Rai</v>
+        <v>Ishwor Shrestha, Junu Aryal</v>
       </c>
       <c r="D5" t="str">
-        <v>078BCT010, 078BCT011, 078BCT012</v>
+        <v>083BCT009, 083BCT010</v>
       </c>
       <c r="E5" t="str">
-        <v>078</v>
+        <v>083</v>
       </c>
       <c r="F5" t="str">
+        <v>NTS</v>
+      </c>
+      <c r="G5" t="str">
         <v/>
       </c>
-      <c r="G5" t="str">
-        <v>Prof. Dr. Hari Bhandari</v>
+      <c r="H5" t="str">
+        <v>Dr. Sabin Wagle</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TeamEpsilon</v>
+        <v>BCT-083-G5</v>
       </c>
       <c r="B6" t="str">
-        <v>Smart Classroom Attendance System</v>
+        <v>Crop Disease Detection Using CNN for Nepali Agriculture</v>
       </c>
       <c r="C6" t="str">
-        <v>Roshan Sharma, Bibek Thapa, Amit Poudel</v>
+        <v>Kishor Chalise, Laxman K.C.</v>
       </c>
       <c r="D6" t="str">
-        <v>078BCT013, 078BCT014, 078BCT015</v>
+        <v>083BCT011, 083BCT012</v>
       </c>
       <c r="E6" t="str">
-        <v>078</v>
+        <v>083</v>
       </c>
       <c r="F6" t="str">
-        <v>Ms. Pooja Acharya</v>
+        <v>EDMES</v>
       </c>
       <c r="G6" t="str">
-        <v>Dr. Sagar Khanal</v>
+        <v>Dr. Nilima Joshi</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
   </ignoredErrors>
 </worksheet>
 </file>